--- a/business_forms/031_project_endorsement_request_form--business_forms.xlsx
+++ b/business_forms/031_project_endorsement_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Endorsement Date</t>
+          <t>Project Endorsment Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_status_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Status 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_status_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Status 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>project_sponsor</t>
+          <t>project_sponsor_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Project Sponsor</t>
+          <t>Project Sponsor 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>project_sponsor_comments</t>
+          <t>project_sponsor_comments_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Project Sponsor Comments</t>
+          <t>Project Sponsor Comments 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_sponsor_choices</t>
+          <t>project_sponsor_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_sponsor_choices</t>
+          <t>project_sponsor_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
